--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69BBE44D-E5B1-422E-9C1A-12AD96084900}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B2A8897-7444-4EEB-BC1B-E873F612D29B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -492,6 +495,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1081,25 +1088,47 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>100</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B2A8897-7444-4EEB-BC1B-E873F612D29B}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{612C385B-3AE0-4731-831C-1908F45445E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1132,25 +1132,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>25</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>2</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>675</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{612C385B-3AE0-4731-831C-1908F45445E9}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E5700AA-6053-4124-8189-0BA9B8AD79C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1176,25 +1179,47 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>23</v>
+      </c>
+      <c r="F10" s="14">
+        <v>400</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>913</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>527</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E5700AA-6053-4124-8189-0BA9B8AD79C5}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6017B9A-2C3B-4BD5-8C16-A5976D84FFAF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1223,25 +1223,47 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14">
+        <v>400</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>90</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>950</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6017B9A-2C3B-4BD5-8C16-A5976D84FFAF}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08CE8CE4-1621-4F3F-92F2-0819E85F44D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1267,25 +1267,47 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>40</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>1070</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08CE8CE4-1621-4F3F-92F2-0819E85F44D0}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACE5F0B-C4F9-41AA-BC8B-EA6B27A56221}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1311,25 +1311,47 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>400</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>55</v>
+      </c>
+      <c r="F13" s="14">
+        <v>195</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACE5F0B-C4F9-41AA-BC8B-EA6B27A56221}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C207C1-CDFC-4960-ACC7-24AE2AC8604D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1355,25 +1355,47 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>300</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>40</v>
+      </c>
+      <c r="F14" s="14">
+        <v>360</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C207C1-CDFC-4960-ACC7-24AE2AC8604D}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5167C437-05DA-4B89-B5C9-DB3F967E28E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1399,25 +1399,47 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>300</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14">
+        <v>20</v>
+      </c>
+      <c r="F15" s="14">
+        <v>450</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5167C437-05DA-4B89-B5C9-DB3F967E28E9}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2278AD5A-BC0A-4AE4-AC35-31E4225DA887}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1443,25 +1443,47 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>350</v>
+      </c>
+      <c r="C16" s="14">
+        <v>120</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2278AD5A-BC0A-4AE4-AC35-31E4225DA887}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D185EFB-0EAE-4050-A26B-C9048362B79D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1487,25 +1487,47 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>300</v>
+      </c>
+      <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>150</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>830</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D185EFB-0EAE-4050-A26B-C9048362B79D}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD76B64-CEC6-473F-9062-EEC23FD9F63E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1531,29 +1531,53 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>100</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>1040</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD76B64-CEC6-473F-9062-EEC23FD9F63E}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2315594-8CC8-4160-8E4A-1E58753E6180}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1578,24 +1578,44 @@
       <c r="A19" s="13">
         <v>46264</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="B19" s="14">
+        <v>340</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>150</v>
+      </c>
+      <c r="E19" s="14">
+        <v>25</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>535</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>905</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2315594-8CC8-4160-8E4A-1E58753E6180}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E331604-450E-4BB7-9F10-429F731A2722}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1619,25 +1619,47 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>340</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E331604-450E-4BB7-9F10-429F731A2722}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0A13C5-E193-4BBD-A531-8C4EEFC6AFEF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1663,25 +1663,47 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>350</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>155</v>
+      </c>
+      <c r="E21" s="14">
+        <v>25</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0A13C5-E193-4BBD-A531-8C4EEFC6AFEF}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D738C31-0993-458A-9F0E-04B9CD246A65}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1707,25 +1707,47 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D738C31-0993-458A-9F0E-04B9CD246A65}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ED9EEFB-16C4-4FF0-B912-84D5A01A84A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1751,25 +1751,47 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>160</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ED9EEFB-16C4-4FF0-B912-84D5A01A84A7}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05F07B4E-9958-48F8-9F13-B6359A045AE4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1795,25 +1795,47 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>320</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>100</v>
+      </c>
+      <c r="E24" s="14">
+        <v>50</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
